--- a/docs/StructureDefinition-BRRegistroImunobiologicoAdministradoCampanha-2.0.xlsx
+++ b/docs/StructureDefinition-BRRegistroImunobiologicoAdministradoCampanha-2.0.xlsx
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -691,7 +691,7 @@
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -790,7 +790,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -868,7 +868,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -941,7 +941,7 @@
     <t>Composition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -978,7 +978,7 @@
     <t>Composition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1257,7 +1257,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1364,7 +1364,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition)</t>
+Reference(Composition|4.0.1)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -1451,7 +1451,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1530,13 +1530,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1622,7 +1622,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1690,7 +1690,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -2040,7 +2040,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="91.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="101.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2197,7 +2197,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>172</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>195</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>210</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>223</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>225</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>319</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>330</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>354</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>469</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>522</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>532</v>
       </c>
@@ -13451,12 +13451,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO97">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
